--- a/data/trans_orig/P34-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P34-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el ejercicio físico que implica su actividad laboral en 2007</t>
+          <t>Población según el ejercicio físico que implica su actividad laboral en 2007 (tasa de respuesta: 99,11%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>56612</t>
+          <t>56821</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>91552</t>
+          <t>89939</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11304</t>
+          <t>10544</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27325</t>
+          <t>26200</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71425</t>
+          <t>72863</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107063</t>
+          <t>110764</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>101598</t>
+          <t>103885</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>143831</t>
+          <t>143759</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38723</t>
+          <t>37881</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66614</t>
+          <t>66436</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>149882</t>
+          <t>148695</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>199707</t>
+          <t>198856</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,45%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>243705</t>
+          <t>241972</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>297418</t>
+          <t>293818</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>411099</t>
+          <t>409619</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>460019</t>
+          <t>457987</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>669191</t>
+          <t>665161</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>740995</t>
+          <t>741303</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>53,85%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>202996</t>
+          <t>203453</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>253142</t>
+          <t>250297</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>161089</t>
+          <t>161218</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>206134</t>
+          <t>204109</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>377817</t>
+          <t>377594</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>444513</t>
+          <t>444815</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,31%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>60800</t>
+          <t>63294</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>95846</t>
+          <t>98382</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35203</t>
+          <t>35374</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>61373</t>
+          <t>62978</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>101441</t>
+          <t>101623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>146751</t>
+          <t>146642</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>130475</t>
+          <t>131092</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>182409</t>
+          <t>177080</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38523</t>
+          <t>39183</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69609</t>
+          <t>68425</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>180097</t>
+          <t>181162</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>236071</t>
+          <t>235506</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>331087</t>
+          <t>330726</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>390868</t>
+          <t>393225</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>547003</t>
+          <t>548449</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>606809</t>
+          <t>607760</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>889472</t>
+          <t>893052</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>987225</t>
+          <t>986146</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,36%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>333410</t>
+          <t>335591</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>394166</t>
+          <t>395416</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>260211</t>
+          <t>257054</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>314514</t>
+          <t>314802</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>605963</t>
+          <t>607536</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>693177</t>
+          <t>693586</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,13%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27475</t>
+          <t>26177</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53202</t>
+          <t>52853</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14961</t>
+          <t>14832</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33198</t>
+          <t>33963</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>44924</t>
+          <t>46996</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>76571</t>
+          <t>79875</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>90895</t>
+          <t>91375</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>129423</t>
+          <t>133856</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32548</t>
+          <t>32592</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>59962</t>
+          <t>59276</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>132094</t>
+          <t>127854</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>179206</t>
+          <t>178224</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,2%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>255198</t>
+          <t>254186</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>303962</t>
+          <t>306387</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>406273</t>
+          <t>406669</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>458137</t>
+          <t>456337</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>677146</t>
+          <t>677097</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>749915</t>
+          <t>748176</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,4%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>220273</t>
+          <t>219094</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>271025</t>
+          <t>271806</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>156814</t>
+          <t>157155</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203698</t>
+          <t>201123</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>389627</t>
+          <t>393699</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>457965</t>
+          <t>462694</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>34,26%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42127</t>
+          <t>43433</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>72901</t>
+          <t>71567</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36716</t>
+          <t>35682</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>64786</t>
+          <t>63210</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>86250</t>
+          <t>86915</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>126552</t>
+          <t>126661</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>112506</t>
+          <t>114772</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>156087</t>
+          <t>157374</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>65927</t>
+          <t>65543</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>99475</t>
+          <t>101310</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>188361</t>
+          <t>189739</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>241442</t>
+          <t>245240</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>285449</t>
+          <t>281484</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>340542</t>
+          <t>341860</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>462994</t>
+          <t>463305</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>527194</t>
+          <t>528046</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>764859</t>
+          <t>767351</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>850761</t>
+          <t>853032</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,76%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>394009</t>
+          <t>391835</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>451733</t>
+          <t>452700</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>364996</t>
+          <t>368555</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>430429</t>
+          <t>431611</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>777177</t>
+          <t>776684</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>864294</t>
+          <t>859917</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,11%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>214810</t>
+          <t>214756</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>274674</t>
+          <t>273749</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>115127</t>
+          <t>114506</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>160534</t>
+          <t>158503</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>343805</t>
+          <t>341636</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>418013</t>
+          <t>418479</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>481763</t>
+          <t>476282</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>565719</t>
+          <t>564738</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>201678</t>
+          <t>199384</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>261238</t>
+          <t>259002</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>698424</t>
+          <t>697578</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>804788</t>
+          <t>801972</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1161728</t>
+          <t>1168790</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1276831</t>
+          <t>1278503</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1875465</t>
+          <t>1885510</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1994159</t>
+          <t>1994784</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3076240</t>
+          <t>3082529</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3244088</t>
+          <t>3239080</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>49,1%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1202725</t>
+          <t>1199176</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1310781</t>
+          <t>1310897</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>997222</t>
+          <t>991252</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1111501</t>
+          <t>1099024</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2236976</t>
+          <t>2229526</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2389398</t>
+          <t>2384239</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,14%</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el ejercicio físico que implica su actividad laboral en 2012</t>
+          <t>Población según el ejercicio físico que implica su actividad laboral en 2012 (tasa de respuesta: 99,28%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27851</t>
+          <t>26791</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52324</t>
+          <t>50972</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11275</t>
+          <t>10988</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31270</t>
+          <t>31130</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57707</t>
+          <t>57995</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70259</t>
+          <t>69212</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>105005</t>
+          <t>105238</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62014</t>
+          <t>62225</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>96718</t>
+          <t>97395</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>140016</t>
+          <t>143069</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>189543</t>
+          <t>196655</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>14,11%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>361884</t>
+          <t>363514</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>415467</t>
+          <t>416136</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>418867</t>
+          <t>420477</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>470949</t>
+          <t>471132</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>799168</t>
+          <t>800569</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>875588</t>
+          <t>874663</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>62,77%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>161728</t>
+          <t>161527</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>212380</t>
+          <t>210922</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>143244</t>
+          <t>144566</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>188391</t>
+          <t>189521</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>318023</t>
+          <t>318622</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>385155</t>
+          <t>381512</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,38%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30189</t>
+          <t>30567</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57357</t>
+          <t>56732</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11082</t>
+          <t>11109</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>34497</t>
+          <t>34056</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>62350</t>
+          <t>62048</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>105685</t>
+          <t>106789</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>150178</t>
+          <t>150798</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>76569</t>
+          <t>77152</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>113704</t>
+          <t>115021</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>193785</t>
+          <t>197070</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>250489</t>
+          <t>252480</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>501394</t>
+          <t>499726</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>568309</t>
+          <t>563532</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>579562</t>
+          <t>576540</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>641926</t>
+          <t>642079</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1096156</t>
+          <t>1095120</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1185191</t>
+          <t>1188377</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>58,15%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>283514</t>
+          <t>284044</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>345299</t>
+          <t>343763</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>290205</t>
+          <t>290125</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>350082</t>
+          <t>351187</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>594048</t>
+          <t>590582</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>674723</t>
+          <t>680204</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,28%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18750</t>
+          <t>18475</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41822</t>
+          <t>40295</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1751</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11374</t>
+          <t>11770</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>24350</t>
+          <t>22431</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>47211</t>
+          <t>46464</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>118154</t>
+          <t>118600</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>164214</t>
+          <t>164386</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>63731</t>
+          <t>62743</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>101708</t>
+          <t>99282</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>192340</t>
+          <t>191352</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>250617</t>
+          <t>248273</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>317620</t>
+          <t>316927</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>372186</t>
+          <t>374516</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>425113</t>
+          <t>423955</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>478689</t>
+          <t>481144</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>760491</t>
+          <t>759520</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>842985</t>
+          <t>842312</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,34%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>214458</t>
+          <t>212473</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>269039</t>
+          <t>267381</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>202000</t>
+          <t>204434</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>255332</t>
+          <t>257148</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>431389</t>
+          <t>433691</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>507106</t>
+          <t>509958</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,5%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19416</t>
+          <t>18604</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40632</t>
+          <t>40923</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19147</t>
+          <t>18733</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27102</t>
+          <t>26806</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>52392</t>
+          <t>50509</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>88022</t>
+          <t>86846</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>130085</t>
+          <t>129332</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>62396</t>
+          <t>62022</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>94800</t>
+          <t>97431</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>160040</t>
+          <t>157765</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>211535</t>
+          <t>211037</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>427906</t>
+          <t>428526</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>492068</t>
+          <t>492573</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>598842</t>
+          <t>597292</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>661880</t>
+          <t>659690</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1044550</t>
+          <t>1044703</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1137217</t>
+          <t>1135562</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>57,45%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>308734</t>
+          <t>308947</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>370158</t>
+          <t>367976</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>295626</t>
+          <t>297439</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>356779</t>
+          <t>357727</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>625441</t>
+          <t>621833</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>709246</t>
+          <t>710261</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,94%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>117186</t>
+          <t>117316</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>162465</t>
+          <t>164705</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14626</t>
+          <t>14318</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>34554</t>
+          <t>35418</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>136803</t>
+          <t>138966</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>187307</t>
+          <t>191464</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>422304</t>
+          <t>421229</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>506767</t>
+          <t>502037</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>294550</t>
+          <t>296233</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>366578</t>
+          <t>362883</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>740852</t>
+          <t>734799</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>853238</t>
+          <t>850138</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1661349</t>
+          <t>1665208</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1788416</t>
+          <t>1786892</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2078388</t>
+          <t>2075545</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2200108</t>
+          <t>2191449</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3775707</t>
+          <t>3784664</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3951242</t>
+          <t>3953873</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>57,01%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1021818</t>
+          <t>1019351</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1134980</t>
+          <t>1135113</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>984494</t>
+          <t>984431</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1093091</t>
+          <t>1096285</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2035403</t>
+          <t>2043008</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2192333</t>
+          <t>2196038</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,66%</t>
         </is>
       </c>
     </row>
@@ -6692,7 +6692,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el ejercicio físico que implica su actividad laboral en 2016</t>
+          <t>Población según el ejercicio físico que implica su actividad laboral en 2016 (tasa de respuesta: 99,41%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8966</t>
+          <t>9462</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27800</t>
+          <t>25899</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7151</t>
+          <t>7279</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11615</t>
+          <t>11464</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28764</t>
+          <t>30593</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51948</t>
+          <t>53720</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83678</t>
+          <t>85005</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29277</t>
+          <t>29131</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54341</t>
+          <t>53944</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>90328</t>
+          <t>91126</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>131651</t>
+          <t>132844</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>342415</t>
+          <t>343851</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>398240</t>
+          <t>392980</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>417837</t>
+          <t>418515</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>469710</t>
+          <t>468190</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>777197</t>
+          <t>778257</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>845898</t>
+          <t>849393</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,5%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>188424</t>
+          <t>189636</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>236929</t>
+          <t>239153</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>160206</t>
+          <t>159208</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>209871</t>
+          <t>206570</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>364614</t>
+          <t>364099</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>430021</t>
+          <t>431133</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14485</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35306</t>
+          <t>33617</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>888</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9643</t>
+          <t>9009</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>17062</t>
+          <t>17385</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>38159</t>
+          <t>38150</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>94608</t>
+          <t>90551</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>135769</t>
+          <t>133933</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54267</t>
+          <t>55506</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>86729</t>
+          <t>88460</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>155808</t>
+          <t>157059</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>213225</t>
+          <t>210364</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>501577</t>
+          <t>504428</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>565005</t>
+          <t>568961</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>649196</t>
+          <t>652259</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>714425</t>
+          <t>714756</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1171099</t>
+          <t>1171933</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1261955</t>
+          <t>1266077</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,66%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>322274</t>
+          <t>317700</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>382324</t>
+          <t>377930</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>252002</t>
+          <t>249436</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>313297</t>
+          <t>308921</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>586680</t>
+          <t>583736</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>670508</t>
+          <t>670796</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,67%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13360</t>
+          <t>12809</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32859</t>
+          <t>32040</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>942</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7928</t>
+          <t>9264</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15278</t>
+          <t>15790</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36372</t>
+          <t>36198</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>81618</t>
+          <t>83515</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>124773</t>
+          <t>123530</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>56118</t>
+          <t>56136</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>88758</t>
+          <t>90067</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>149056</t>
+          <t>149772</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>201068</t>
+          <t>200129</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,01%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>342144</t>
+          <t>341280</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>399929</t>
+          <t>396431</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>408435</t>
+          <t>411619</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>466629</t>
+          <t>468443</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>768932</t>
+          <t>768950</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>848796</t>
+          <t>844753</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>54,9%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>234666</t>
+          <t>234941</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>291194</t>
+          <t>288887</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>242540</t>
+          <t>243901</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>298213</t>
+          <t>298464</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>496914</t>
+          <t>495624</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>571716</t>
+          <t>570109</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,05%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21015</t>
+          <t>19833</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>43008</t>
+          <t>42335</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3684</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15739</t>
+          <t>16086</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26926</t>
+          <t>27179</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>52889</t>
+          <t>52289</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>89566</t>
+          <t>89082</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>127589</t>
+          <t>126425</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>65027</t>
+          <t>66361</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>99822</t>
+          <t>99209</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>163782</t>
+          <t>164840</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>215161</t>
+          <t>214804</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>353709</t>
+          <t>353211</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>412207</t>
+          <t>411443</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>539268</t>
+          <t>540577</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>604998</t>
+          <t>608316</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>909813</t>
+          <t>911483</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>999850</t>
+          <t>1005140</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>51,09%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>379195</t>
+          <t>377804</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>438557</t>
+          <t>439638</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>344135</t>
+          <t>339670</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>409295</t>
+          <t>408118</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>743133</t>
+          <t>738927</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>831521</t>
+          <t>828411</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,11%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>73562</t>
+          <t>72220</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>112134</t>
+          <t>110704</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9466</t>
+          <t>10743</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26459</t>
+          <t>27503</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>88477</t>
+          <t>87168</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>130563</t>
+          <t>129944</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>351628</t>
+          <t>350639</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>425571</t>
+          <t>427176</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>234671</t>
+          <t>237509</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>298561</t>
+          <t>302649</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>608183</t>
+          <t>606402</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>704808</t>
+          <t>703314</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1591576</t>
+          <t>1592660</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1710324</t>
+          <t>1714376</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2076917</t>
+          <t>2077053</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2195655</t>
+          <t>2192127</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9444,7 +9444,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3709505</t>
+          <t>3717770</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3891565</t>
+          <t>3887219</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>56,36%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1176708</t>
+          <t>1176528</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1288413</t>
+          <t>1285977</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1050438</t>
+          <t>1053437</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1166216</t>
+          <t>1165455</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2253866</t>
+          <t>2264810</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2414972</t>
+          <t>2421900</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>35,12%</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9769,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el ejercicio físico que implica su actividad laboral en 2023</t>
+          <t>Población según el ejercicio físico que implica su actividad laboral en 2023 (tasa de respuesta: 99,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9964,12 +9964,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52118</t>
+          <t>52579</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>83798</t>
+          <t>85326</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12527</t>
+          <t>12788</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27456</t>
+          <t>26805</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>70470</t>
+          <t>68886</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>108149</t>
+          <t>105125</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -10077,12 +10077,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>133100</t>
+          <t>134055</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>177957</t>
+          <t>178977</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>117995</t>
+          <t>117280</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>151225</t>
+          <t>152720</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>261965</t>
+          <t>261554</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>319354</t>
+          <t>317833</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,37%</t>
         </is>
       </c>
     </row>
@@ -10190,12 +10190,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>200597</t>
+          <t>199372</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>256455</t>
+          <t>257515</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>293054</t>
+          <t>293081</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>333162</t>
+          <t>334961</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10245,7 +10245,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>506825</t>
+          <t>505487</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>572209</t>
+          <t>575154</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>44,1%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>159611</t>
+          <t>161074</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>206007</t>
+          <t>209186</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>190762</t>
+          <t>190281</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>226675</t>
+          <t>225796</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>359907</t>
+          <t>361767</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>420552</t>
+          <t>421702</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,33%</t>
         </is>
       </c>
     </row>
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40088</t>
+          <t>32204</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>101008</t>
+          <t>100158</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16377</t>
+          <t>16896</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33038</t>
+          <t>33536</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>63430</t>
+          <t>62609</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>121832</t>
+          <t>119386</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -10646,12 +10646,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>234093</t>
+          <t>231411</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>770310</t>
+          <t>762458</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>159663</t>
+          <t>158602</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>201025</t>
+          <t>201768</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>408352</t>
+          <t>415051</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1096798</t>
+          <t>1185465</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>55,53%</t>
         </is>
       </c>
     </row>
@@ -10759,12 +10759,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>178463</t>
+          <t>195918</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>435577</t>
+          <t>438278</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10774,12 +10774,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>410280</t>
+          <t>409804</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>463478</t>
+          <t>461857</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>518839</t>
+          <t>471449</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>882214</t>
+          <t>882872</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,36%</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>182502</t>
+          <t>187681</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>437108</t>
+          <t>433001</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>289949</t>
+          <t>290118</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>339601</t>
+          <t>338942</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>443377</t>
+          <t>428145</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>747414</t>
+          <t>744367</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,87%</t>
         </is>
       </c>
     </row>
@@ -11102,12 +11102,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16193</t>
+          <t>14984</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38910</t>
+          <t>35279</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11117,12 +11117,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>5329</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20234</t>
+          <t>21257</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11152,12 +11152,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>22177</t>
+          <t>22645</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>52761</t>
+          <t>53156</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>119452</t>
+          <t>118917</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>174061</t>
+          <t>173183</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>60493</t>
+          <t>65400</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>164087</t>
+          <t>164997</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11265,12 +11265,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>173066</t>
+          <t>169371</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>318132</t>
+          <t>318489</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11300,12 +11300,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,54%</t>
         </is>
       </c>
     </row>
@@ -11328,12 +11328,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>246291</t>
+          <t>249050</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>309057</t>
+          <t>312349</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>444910</t>
+          <t>448248</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>737767</t>
+          <t>720699</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11378,12 +11378,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>711548</t>
+          <t>704985</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1108718</t>
+          <t>1138011</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11413,12 +11413,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>69,81%</t>
         </is>
       </c>
     </row>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>224943</t>
+          <t>222579</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>282379</t>
+          <t>280722</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>126597</t>
+          <t>127534</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>312277</t>
+          <t>308376</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11491,12 +11491,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>315983</t>
+          <t>306981</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>568219</t>
+          <t>571931</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>35,08%</t>
         </is>
       </c>
     </row>
@@ -11671,12 +11671,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37833</t>
+          <t>38274</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>67917</t>
+          <t>67364</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11686,12 +11686,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9477</t>
+          <t>9490</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24350</t>
+          <t>24363</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>52066</t>
+          <t>51746</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>85625</t>
+          <t>85608</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11756,7 +11756,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>121117</t>
+          <t>123130</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>167886</t>
+          <t>168856</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>117170</t>
+          <t>118323</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>376816</t>
+          <t>372237</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>258753</t>
+          <t>259088</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>523209</t>
+          <t>527361</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,32%</t>
         </is>
       </c>
     </row>
@@ -11897,12 +11897,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>287075</t>
+          <t>289403</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>349229</t>
+          <t>349902</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>381720</t>
+          <t>388451</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>527577</t>
+          <t>526978</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11947,12 +11947,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>714297</t>
+          <t>709420</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>850051</t>
+          <t>855309</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,7%</t>
         </is>
       </c>
     </row>
@@ -12010,12 +12010,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>367877</t>
+          <t>369400</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>436377</t>
+          <t>433989</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12025,12 +12025,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>325513</t>
+          <t>315825</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>443914</t>
+          <t>445010</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12060,12 +12060,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>707893</t>
+          <t>719617</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>858393</t>
+          <t>858468</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12095,7 +12095,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>168303</t>
+          <t>164165</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>252320</t>
+          <t>250254</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12255,12 +12255,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>53806</t>
+          <t>55124</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>86815</t>
+          <t>86310</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12290,12 +12290,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>240783</t>
+          <t>241008</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>325241</t>
+          <t>325167</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>664016</t>
+          <t>670944</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1428896</t>
+          <t>1473787</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>521387</t>
+          <t>522474</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>803198</t>
+          <t>806954</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1252140</t>
+          <t>1237236</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2227284</t>
+          <t>2223442</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,44%</t>
         </is>
       </c>
     </row>
@@ -12466,12 +12466,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>905228</t>
+          <t>906828</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1277735</t>
+          <t>1274225</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12481,12 +12481,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1647572</t>
+          <t>1650938</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2153827</t>
+          <t>2149960</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12516,12 +12516,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2670195</t>
+          <t>2674236</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3336087</t>
+          <t>3328205</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>47,06%</t>
         </is>
       </c>
     </row>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>915087</t>
+          <t>901102</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1278003</t>
+          <t>1283309</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12594,12 +12594,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>894759</t>
+          <t>934042</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1251040</t>
+          <t>1254027</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1981041</t>
+          <t>2003416</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2495516</t>
+          <t>2488184</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,18%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P34-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P34-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>56821</t>
+          <t>56115</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>89939</t>
+          <t>89398</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10544</t>
+          <t>10692</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26200</t>
+          <t>26030</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>72863</t>
+          <t>71881</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>110764</t>
+          <t>106373</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>103885</t>
+          <t>101388</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>143759</t>
+          <t>141848</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37881</t>
+          <t>38461</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66436</t>
+          <t>65122</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>148695</t>
+          <t>148052</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>198856</t>
+          <t>200453</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>241972</t>
+          <t>245304</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>293818</t>
+          <t>297021</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>409619</t>
+          <t>408640</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>457987</t>
+          <t>458399</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>665161</t>
+          <t>664333</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>741303</t>
+          <t>736688</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>53,52%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>203453</t>
+          <t>202134</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>250297</t>
+          <t>251183</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>161218</t>
+          <t>161254</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>204109</t>
+          <t>207187</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>377594</t>
+          <t>376542</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>444815</t>
+          <t>441520</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,07%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63294</t>
+          <t>61702</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>98382</t>
+          <t>95081</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35374</t>
+          <t>34288</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62978</t>
+          <t>59954</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>101623</t>
+          <t>101400</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>146642</t>
+          <t>145432</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>131092</t>
+          <t>133048</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>177080</t>
+          <t>179513</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39183</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68425</t>
+          <t>68223</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>181162</t>
+          <t>179385</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>235506</t>
+          <t>237424</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,37%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>330726</t>
+          <t>331428</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>393225</t>
+          <t>394856</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>548449</t>
+          <t>548635</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>607760</t>
+          <t>608078</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>893052</t>
+          <t>898604</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>986146</t>
+          <t>988905</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,51%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>335591</t>
+          <t>333314</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>395416</t>
+          <t>392447</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>257054</t>
+          <t>259738</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>314802</t>
+          <t>313585</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>607536</t>
+          <t>606579</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>693586</t>
+          <t>692396</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,06%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>26177</t>
+          <t>26816</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>52853</t>
+          <t>51050</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14832</t>
+          <t>13937</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33963</t>
+          <t>33310</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>46996</t>
+          <t>47481</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>79875</t>
+          <t>78124</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>91375</t>
+          <t>90523</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>133856</t>
+          <t>130123</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32592</t>
+          <t>32969</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>59276</t>
+          <t>58881</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>127854</t>
+          <t>130938</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>178224</t>
+          <t>180020</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>254186</t>
+          <t>252688</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>306387</t>
+          <t>304455</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>406669</t>
+          <t>407387</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>456337</t>
+          <t>455906</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>677097</t>
+          <t>675798</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>748176</t>
+          <t>751622</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>55,66%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>219094</t>
+          <t>221179</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>271806</t>
+          <t>270926</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>157155</t>
+          <t>159149</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>201123</t>
+          <t>203967</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>393699</t>
+          <t>390498</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>462694</t>
+          <t>459675</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,04%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>43433</t>
+          <t>43089</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>71567</t>
+          <t>70732</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35682</t>
+          <t>36195</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63210</t>
+          <t>63549</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>86915</t>
+          <t>87329</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>126661</t>
+          <t>126737</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>114772</t>
+          <t>114472</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>157374</t>
+          <t>157421</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>65543</t>
+          <t>65534</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>101310</t>
+          <t>100269</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>189739</t>
+          <t>189962</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>245240</t>
+          <t>243280</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>281484</t>
+          <t>283171</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>341860</t>
+          <t>342632</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>463305</t>
+          <t>461512</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>528046</t>
+          <t>524958</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>767351</t>
+          <t>764577</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>853032</t>
+          <t>848970</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>43,55%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>391835</t>
+          <t>392735</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>452700</t>
+          <t>452432</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>368555</t>
+          <t>367982</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>431611</t>
+          <t>428985</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,47 +2829,47 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
+          <t>41,88%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>841</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>821410</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>778696</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>866481</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
           <t>42,14%</t>
         </is>
       </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>841</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>821410</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>776684</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>859917</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>42,14%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,45%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>214756</t>
+          <t>214307</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>273749</t>
+          <t>276947</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>114506</t>
+          <t>115655</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>158503</t>
+          <t>161815</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>341636</t>
+          <t>343388</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>418479</t>
+          <t>417572</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>476282</t>
+          <t>482245</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>564738</t>
+          <t>567273</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>199384</t>
+          <t>202875</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>259002</t>
+          <t>260733</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>697578</t>
+          <t>700140</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>801972</t>
+          <t>802117</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1168790</t>
+          <t>1170336</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1278503</t>
+          <t>1281250</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1885510</t>
+          <t>1884086</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1994784</t>
+          <t>1999591</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3082529</t>
+          <t>3081151</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3239080</t>
+          <t>3243731</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>49,17%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1199176</t>
+          <t>1201843</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1310897</t>
+          <t>1314838</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>991252</t>
+          <t>990333</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1099024</t>
+          <t>1100891</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2229526</t>
+          <t>2232445</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2384239</t>
+          <t>2386107</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,17%</t>
         </is>
       </c>
     </row>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26791</t>
+          <t>27730</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50972</t>
+          <t>52611</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10988</t>
+          <t>10131</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31130</t>
+          <t>31053</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57995</t>
+          <t>57835</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69212</t>
+          <t>70046</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>105238</t>
+          <t>106240</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62225</t>
+          <t>59490</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>97395</t>
+          <t>96177</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>143069</t>
+          <t>141158</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>196655</t>
+          <t>189323</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,59%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>363514</t>
+          <t>360387</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>416136</t>
+          <t>414537</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>420477</t>
+          <t>423405</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>471132</t>
+          <t>475836</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>800569</t>
+          <t>802479</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>874663</t>
+          <t>872095</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,59%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>161527</t>
+          <t>162154</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>210922</t>
+          <t>208334</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>144566</t>
+          <t>141545</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>189521</t>
+          <t>187598</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>318622</t>
+          <t>316828</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>381512</t>
+          <t>380445</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,3%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30567</t>
+          <t>30422</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56732</t>
+          <t>56570</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>1969</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11109</t>
+          <t>11177</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>34056</t>
+          <t>35483</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>62048</t>
+          <t>63032</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>106789</t>
+          <t>106497</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>150798</t>
+          <t>149524</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>77152</t>
+          <t>75945</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>115021</t>
+          <t>114991</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>197070</t>
+          <t>196567</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>252480</t>
+          <t>254835</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>499726</t>
+          <t>498678</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>563532</t>
+          <t>566971</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>576540</t>
+          <t>578324</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>642079</t>
+          <t>641192</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1095120</t>
+          <t>1096578</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1188377</t>
+          <t>1188191</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>53,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,14%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>284044</t>
+          <t>282757</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>343763</t>
+          <t>342743</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>290125</t>
+          <t>289103</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>351187</t>
+          <t>351182</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>590582</t>
+          <t>588256</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>680204</t>
+          <t>676862</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,12%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18475</t>
+          <t>18264</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40295</t>
+          <t>40536</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11770</t>
+          <t>12367</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>23595</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46464</t>
+          <t>46629</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>118600</t>
+          <t>117965</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>164386</t>
+          <t>162920</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>62743</t>
+          <t>65050</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>99282</t>
+          <t>102036</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>191352</t>
+          <t>194103</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>248273</t>
+          <t>250958</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,49%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>316927</t>
+          <t>315909</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>374516</t>
+          <t>371600</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>423955</t>
+          <t>427054</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>481144</t>
+          <t>486892</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>759520</t>
+          <t>755709</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>842312</t>
+          <t>843329</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,41%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>212473</t>
+          <t>212886</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>267381</t>
+          <t>266270</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>204434</t>
+          <t>197648</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>257148</t>
+          <t>254802</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>433691</t>
+          <t>428772</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>509958</t>
+          <t>508203</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,39%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18604</t>
+          <t>19413</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40923</t>
+          <t>40637</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18733</t>
+          <t>18573</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26806</t>
+          <t>26638</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>50509</t>
+          <t>52179</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>86846</t>
+          <t>87162</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>129332</t>
+          <t>126452</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>62022</t>
+          <t>62226</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>97431</t>
+          <t>96804</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>157765</t>
+          <t>159513</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>211037</t>
+          <t>212300</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>428526</t>
+          <t>428956</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>492573</t>
+          <t>493788</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>597292</t>
+          <t>590845</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>659690</t>
+          <t>662072</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1044703</t>
+          <t>1041298</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1135562</t>
+          <t>1136138</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>57,48%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>308947</t>
+          <t>309707</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>367976</t>
+          <t>371843</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>297439</t>
+          <t>295831</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>357727</t>
+          <t>361491</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>621833</t>
+          <t>617865</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>710261</t>
+          <t>707022</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>35,77%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>117316</t>
+          <t>115233</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>164705</t>
+          <t>164024</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14318</t>
+          <t>15299</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>35418</t>
+          <t>35172</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>138966</t>
+          <t>137063</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>191464</t>
+          <t>187614</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>421229</t>
+          <t>420525</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>502037</t>
+          <t>501866</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>296233</t>
+          <t>295721</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>362883</t>
+          <t>365684</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>734799</t>
+          <t>731576</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>850138</t>
+          <t>843473</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1665208</t>
+          <t>1671798</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1786892</t>
+          <t>1794116</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2075545</t>
+          <t>2073841</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2191449</t>
+          <t>2197609</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3784664</t>
+          <t>3776632</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3953873</t>
+          <t>3951470</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>56,97%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1019351</t>
+          <t>1016604</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1135113</t>
+          <t>1132814</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>984431</t>
+          <t>982008</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1096285</t>
+          <t>1097563</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2043008</t>
+          <t>2035447</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2196038</t>
+          <t>2198933</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,71%</t>
         </is>
       </c>
     </row>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9462</t>
+          <t>9888</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25899</t>
+          <t>27023</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>823</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7279</t>
+          <t>7363</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11464</t>
+          <t>11662</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30593</t>
+          <t>30143</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53720</t>
+          <t>53561</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>85005</t>
+          <t>85535</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29131</t>
+          <t>30433</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53944</t>
+          <t>55377</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>91126</t>
+          <t>88836</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>132844</t>
+          <t>128793</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>343851</t>
+          <t>344406</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>392980</t>
+          <t>396779</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>418515</t>
+          <t>417768</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>468190</t>
+          <t>465392</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>778257</t>
+          <t>778296</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>849393</t>
+          <t>846693</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,3%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>189636</t>
+          <t>188656</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>239153</t>
+          <t>237419</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>159208</t>
+          <t>161959</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>206570</t>
+          <t>207751</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>364099</t>
+          <t>365706</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>431133</t>
+          <t>427607</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>31,97%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15046</t>
+          <t>14979</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33617</t>
+          <t>35698</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9009</t>
+          <t>8822</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7511,42 +7511,42 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>26502</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>17767</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>39871</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>0,87%</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>26502</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>17385</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>38150</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>90551</t>
+          <t>91201</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>133933</t>
+          <t>135090</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55506</t>
+          <t>56397</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88460</t>
+          <t>89071</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>157059</t>
+          <t>157872</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>210364</t>
+          <t>212794</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>504428</t>
+          <t>504434</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>568961</t>
+          <t>567615</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>652259</t>
+          <t>653490</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>714756</t>
+          <t>713933</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1171933</t>
+          <t>1174341</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1266077</t>
+          <t>1267428</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,73%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>317700</t>
+          <t>316566</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>377930</t>
+          <t>378303</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>249436</t>
+          <t>249715</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>308921</t>
+          <t>305677</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>583736</t>
+          <t>582496</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>670796</t>
+          <t>667577</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,51%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12809</t>
+          <t>13039</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32040</t>
+          <t>32008</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>945</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9264</t>
+          <t>8257</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15790</t>
+          <t>15614</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36198</t>
+          <t>36209</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>83515</t>
+          <t>84226</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>123530</t>
+          <t>122973</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>56136</t>
+          <t>56861</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>90067</t>
+          <t>89372</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>149772</t>
+          <t>150711</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>200129</t>
+          <t>199437</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>341280</t>
+          <t>340404</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>396431</t>
+          <t>398879</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>411619</t>
+          <t>409179</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>468443</t>
+          <t>466324</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>768950</t>
+          <t>767699</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>844753</t>
+          <t>846250</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>55,0%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>234941</t>
+          <t>235220</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>288887</t>
+          <t>292702</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>243901</t>
+          <t>245365</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>298464</t>
+          <t>299209</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>495624</t>
+          <t>495421</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>570109</t>
+          <t>574174</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,32%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19833</t>
+          <t>21570</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>42335</t>
+          <t>45529</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16086</t>
+          <t>16052</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27179</t>
+          <t>26925</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>52289</t>
+          <t>52627</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>89082</t>
+          <t>88593</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>126425</t>
+          <t>125689</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>66361</t>
+          <t>67352</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>99209</t>
+          <t>100388</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>164840</t>
+          <t>164789</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>214804</t>
+          <t>219269</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8797,7 +8797,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>353211</t>
+          <t>350509</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>411443</t>
+          <t>411234</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>540577</t>
+          <t>538858</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608316</t>
+          <t>606881</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>911483</t>
+          <t>915927</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1005140</t>
+          <t>1002915</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>50,98%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>377804</t>
+          <t>379935</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>439638</t>
+          <t>438559</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>339670</t>
+          <t>341882</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>408118</t>
+          <t>407991</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>738927</t>
+          <t>739399</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>828411</t>
+          <t>825531</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>41,96%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>72220</t>
+          <t>72868</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>110704</t>
+          <t>110921</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,7 +9178,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10743</t>
+          <t>10565</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>27503</t>
+          <t>27560</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>87168</t>
+          <t>88176</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>129944</t>
+          <t>130538</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>350639</t>
+          <t>350618</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>427176</t>
+          <t>428379</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9296,7 +9296,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>237509</t>
+          <t>236152</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>302649</t>
+          <t>300053</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>606402</t>
+          <t>604889</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>703314</t>
+          <t>704438</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1592660</t>
+          <t>1599559</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1714376</t>
+          <t>1716649</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2077053</t>
+          <t>2079933</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2192127</t>
+          <t>2194128</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3717770</t>
+          <t>3715129</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3887219</t>
+          <t>3878956</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>56,24%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1176528</t>
+          <t>1178230</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1285977</t>
+          <t>1290234</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1053437</t>
+          <t>1055134</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1165455</t>
+          <t>1163741</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2264810</t>
+          <t>2257890</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2421900</t>
+          <t>2417589</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,05%</t>
         </is>
       </c>
     </row>
@@ -9959,32 +9959,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>67858</t>
+          <t>71997</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52579</t>
+          <t>56501</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>85326</t>
+          <t>89776</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9994,32 +9994,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>18898</t>
+          <t>19522</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12788</t>
+          <t>13766</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26805</t>
+          <t>28435</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10029,32 +10029,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>86756</t>
+          <t>91519</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>68886</t>
+          <t>73694</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>105125</t>
+          <t>112073</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -10072,32 +10072,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>154279</t>
+          <t>176182</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>134055</t>
+          <t>152687</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>178977</t>
+          <t>203024</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10107,32 +10107,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>133560</t>
+          <t>149566</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>117280</t>
+          <t>131372</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>152720</t>
+          <t>168859</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10142,32 +10142,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>287839</t>
+          <t>325748</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>261554</t>
+          <t>295980</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>317833</t>
+          <t>357362</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>25,25%</t>
         </is>
       </c>
     </row>
@@ -10185,32 +10185,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>226380</t>
+          <t>238420</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>199372</t>
+          <t>211005</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>257515</t>
+          <t>267001</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10220,32 +10220,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>312422</t>
+          <t>334013</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>293081</t>
+          <t>313554</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>334961</t>
+          <t>356551</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10255,32 +10255,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>538802</t>
+          <t>572432</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>505487</t>
+          <t>539633</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>575154</t>
+          <t>609959</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>43,09%</t>
         </is>
       </c>
     </row>
@@ -10298,32 +10298,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>182908</t>
+          <t>199481</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>161074</t>
+          <t>176140</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>209186</t>
+          <t>224780</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10333,32 +10333,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>207953</t>
+          <t>226365</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>190281</t>
+          <t>205649</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>225796</t>
+          <t>246288</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10368,32 +10368,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>390861</t>
+          <t>425846</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>361767</t>
+          <t>391536</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>421702</t>
+          <t>455795</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,2%</t>
         </is>
       </c>
     </row>
@@ -10411,17 +10411,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>631426</t>
+          <t>686080</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>631426</t>
+          <t>686080</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>631426</t>
+          <t>686080</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10446,17 +10446,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>672832</t>
+          <t>729465</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>672832</t>
+          <t>729465</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>672832</t>
+          <t>729465</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10481,17 +10481,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1304258</t>
+          <t>1415545</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1304258</t>
+          <t>1415545</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1304258</t>
+          <t>1415545</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10528,32 +10528,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>72524</t>
+          <t>87204</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32204</t>
+          <t>69280</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>100158</t>
+          <t>108813</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10563,22 +10563,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24006</t>
+          <t>27033</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16896</t>
+          <t>18836</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33536</t>
+          <t>36583</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10598,32 +10598,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>96531</t>
+          <t>114238</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>62609</t>
+          <t>91889</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>119386</t>
+          <t>137274</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -10641,32 +10641,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>437655</t>
+          <t>215261</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>231411</t>
+          <t>187244</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>762458</t>
+          <t>244468</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10676,32 +10676,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>179939</t>
+          <t>202384</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>158602</t>
+          <t>180112</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>201768</t>
+          <t>228315</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10711,32 +10711,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>617594</t>
+          <t>417645</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>415051</t>
+          <t>384156</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1185465</t>
+          <t>456402</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>21,68%</t>
         </is>
       </c>
     </row>
@@ -10754,32 +10754,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>336749</t>
+          <t>379121</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>195918</t>
+          <t>341839</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>438278</t>
+          <t>413382</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10789,32 +10789,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>435397</t>
+          <t>485126</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>409804</t>
+          <t>456119</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>461857</t>
+          <t>512293</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10824,32 +10824,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>772146</t>
+          <t>864247</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>471449</t>
+          <t>820460</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>882872</t>
+          <t>907774</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>43,13%</t>
         </is>
       </c>
     </row>
@@ -10867,32 +10867,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>333649</t>
+          <t>356608</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>187681</t>
+          <t>320251</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>433001</t>
+          <t>393794</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10902,32 +10902,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>314733</t>
+          <t>352072</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>290118</t>
+          <t>325210</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>338942</t>
+          <t>382051</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10937,32 +10937,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>648382</t>
+          <t>708680</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>428145</t>
+          <t>665803</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>744367</t>
+          <t>753499</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>35,8%</t>
         </is>
       </c>
     </row>
@@ -10980,17 +10980,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1180577</t>
+          <t>1038194</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1180577</t>
+          <t>1038194</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1180577</t>
+          <t>1038194</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11015,17 +11015,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>954076</t>
+          <t>1066616</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>954076</t>
+          <t>1066616</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>954076</t>
+          <t>1066616</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11050,17 +11050,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2134653</t>
+          <t>2104810</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2134653</t>
+          <t>2104810</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2134653</t>
+          <t>2104810</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11097,32 +11097,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>24268</t>
+          <t>36326</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14984</t>
+          <t>22709</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35279</t>
+          <t>56705</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11132,32 +11132,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>11794</t>
+          <t>15203</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5329</t>
+          <t>9191</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21257</t>
+          <t>25282</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11167,32 +11167,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>36062</t>
+          <t>51529</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>22645</t>
+          <t>36216</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>53156</t>
+          <t>73387</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -11210,32 +11210,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>145816</t>
+          <t>179754</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>118917</t>
+          <t>153045</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>173183</t>
+          <t>209330</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11245,32 +11245,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>121053</t>
+          <t>139270</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>65400</t>
+          <t>120126</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>164997</t>
+          <t>161074</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11280,32 +11280,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>266868</t>
+          <t>319024</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>169371</t>
+          <t>283753</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>318489</t>
+          <t>351041</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -11323,32 +11323,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>277837</t>
+          <t>308183</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>249050</t>
+          <t>276497</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>312349</t>
+          <t>340089</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11358,32 +11358,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>565532</t>
+          <t>385601</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>448248</t>
+          <t>358098</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>720699</t>
+          <t>413030</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11393,32 +11393,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>843370</t>
+          <t>693784</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>704985</t>
+          <t>658045</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1138011</t>
+          <t>738395</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>46,01%</t>
         </is>
       </c>
     </row>
@@ -11436,32 +11436,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>252198</t>
+          <t>273973</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>222579</t>
+          <t>245319</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>280722</t>
+          <t>305038</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11471,32 +11471,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>231719</t>
+          <t>266408</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>127534</t>
+          <t>240345</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>308376</t>
+          <t>290821</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11506,32 +11506,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>483917</t>
+          <t>540381</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>306981</t>
+          <t>503125</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>571931</t>
+          <t>581105</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>36,21%</t>
         </is>
       </c>
     </row>
@@ -11549,17 +11549,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>700119</t>
+          <t>798235</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>700119</t>
+          <t>798235</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>700119</t>
+          <t>798235</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11584,17 +11584,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>930097</t>
+          <t>806483</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>930097</t>
+          <t>806483</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>930097</t>
+          <t>806483</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11619,17 +11619,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1630217</t>
+          <t>1604718</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1630217</t>
+          <t>1604718</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1630217</t>
+          <t>1604718</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11666,32 +11666,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>51327</t>
+          <t>59051</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38274</t>
+          <t>44264</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>67364</t>
+          <t>77331</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11701,32 +11701,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15472</t>
+          <t>16415</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9490</t>
+          <t>10311</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24363</t>
+          <t>25100</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11736,32 +11736,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>66798</t>
+          <t>75467</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>51746</t>
+          <t>58661</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>85608</t>
+          <t>94267</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -11779,32 +11779,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>144799</t>
+          <t>163669</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>123130</t>
+          <t>139106</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>168856</t>
+          <t>190102</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11814,32 +11814,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>184759</t>
+          <t>127808</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>118323</t>
+          <t>109840</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>372237</t>
+          <t>148502</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11849,32 +11849,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>329559</t>
+          <t>291477</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>259088</t>
+          <t>261336</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>527361</t>
+          <t>322828</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>15,44%</t>
         </is>
       </c>
     </row>
@@ -11892,32 +11892,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>318916</t>
+          <t>344011</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>289403</t>
+          <t>314311</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>349902</t>
+          <t>378592</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11927,32 +11927,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>482054</t>
+          <t>531061</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>388451</t>
+          <t>499352</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>526978</t>
+          <t>559763</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11962,32 +11962,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>800970</t>
+          <t>875071</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>709420</t>
+          <t>832541</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>855309</t>
+          <t>919962</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>44,01%</t>
         </is>
       </c>
     </row>
@@ -12005,32 +12005,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>400931</t>
+          <t>412443</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>369400</t>
+          <t>378434</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>433989</t>
+          <t>445922</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12040,32 +12040,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>405039</t>
+          <t>435804</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>315825</t>
+          <t>405457</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>445010</t>
+          <t>468269</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12075,32 +12075,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>805971</t>
+          <t>848246</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>719617</t>
+          <t>806898</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>858468</t>
+          <t>895844</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,86%</t>
         </is>
       </c>
     </row>
@@ -12118,17 +12118,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>915973</t>
+          <t>979174</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>915973</t>
+          <t>979174</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>915973</t>
+          <t>979174</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12153,17 +12153,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1087324</t>
+          <t>1111088</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1087324</t>
+          <t>1111088</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1087324</t>
+          <t>1111088</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12188,17 +12188,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2003298</t>
+          <t>2090261</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2003298</t>
+          <t>2090261</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2003298</t>
+          <t>2090261</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12235,32 +12235,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>215978</t>
+          <t>254579</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>164165</t>
+          <t>222595</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>250254</t>
+          <t>291282</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12270,32 +12270,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>70169</t>
+          <t>78173</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>55124</t>
+          <t>64650</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>86310</t>
+          <t>95910</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12305,32 +12305,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>286147</t>
+          <t>332752</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>241008</t>
+          <t>296812</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>325167</t>
+          <t>371835</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -12348,32 +12348,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>882549</t>
+          <t>734866</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>670944</t>
+          <t>684038</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1473787</t>
+          <t>788940</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12383,32 +12383,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>619311</t>
+          <t>619028</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>522474</t>
+          <t>575563</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>806954</t>
+          <t>659066</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12418,32 +12418,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1501860</t>
+          <t>1353894</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1237236</t>
+          <t>1290486</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2223442</t>
+          <t>1420531</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>19,69%</t>
         </is>
       </c>
     </row>
@@ -12461,32 +12461,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1159883</t>
+          <t>1269733</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>906828</t>
+          <t>1206652</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1274225</t>
+          <t>1334807</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12496,32 +12496,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1795405</t>
+          <t>1735802</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1650938</t>
+          <t>1676410</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2149960</t>
+          <t>1790919</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12531,32 +12531,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2955288</t>
+          <t>3005535</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2674236</t>
+          <t>2919802</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3328205</t>
+          <t>3091001</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>42,84%</t>
         </is>
       </c>
     </row>
@@ -12574,32 +12574,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1169687</t>
+          <t>1242504</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>901102</t>
+          <t>1182991</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1283309</t>
+          <t>1309316</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12609,32 +12609,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1159445</t>
+          <t>1280649</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>934042</t>
+          <t>1229569</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1254027</t>
+          <t>1334690</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12644,32 +12644,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2329131</t>
+          <t>2523153</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2003416</t>
+          <t>2448324</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2488184</t>
+          <t>2609032</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>36,16%</t>
         </is>
       </c>
     </row>
@@ -12687,17 +12687,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3428096</t>
+          <t>3501682</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3428096</t>
+          <t>3501682</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3428096</t>
+          <t>3501682</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12722,17 +12722,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3644330</t>
+          <t>3713652</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3644330</t>
+          <t>3713652</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3644330</t>
+          <t>3713652</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12757,17 +12757,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7072426</t>
+          <t>7215335</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7072426</t>
+          <t>7215335</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7072426</t>
+          <t>7215335</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
